--- a/Mass_update_DOSIsoft/mass_update_DOSIsoft_hierarchy_fix.xlsx
+++ b/Mass_update_DOSIsoft/mass_update_DOSIsoft_hierarchy_fix.xlsx
@@ -527,7 +527,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>a0RQQ00000IQxoV</t>
+          <t>a0RQQ00000IQxoW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -559,7 +559,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>a0RQQ00000IQxoW</t>
+          <t>a0RQQ00000IEdIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>a0RQQ00000IEdIS</t>
+          <t>a0RQQ00000IQxoV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -687,7 +687,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>a0RQQ00000IEdPB</t>
+          <t>a0RQQ00000IQxoY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>a0RQQ00000IQxoY</t>
+          <t>a0RQQ00000IEdPB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/Mass_update_DOSIsoft/mass_update_DOSIsoft_hierarchy_fix.xlsx
+++ b/Mass_update_DOSIsoft/mass_update_DOSIsoft_hierarchy_fix.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,30 +463,158 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>a0RQQ00000MIyyj</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>a0R6g00000DLAtn</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>a0R6g00000DLAtn</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>DOSIsoft HW</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>C#89565</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>30005138_DOS001_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MIyyk</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>a0R6g00000DLAtn</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>a0R6g00000DLAtn</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>DOSIsoft HW</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>C#89565</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>30005138_DOS001_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MIyyl</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>a0R6g00000DLAtn</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>a0R6g00000DLAtn</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>THINKQA FOR LINAC</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>C#89549-20</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30005138_DOS001_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MIyym</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>a0R6g00000DLAtn</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>a0R6g00000DLAtn</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>THINKQA FOR LINAC</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>C#89549-20</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30005138_DOS001_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>a0RQQ00000LcAQU</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>a0RQQ00000HbOrB</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>a0RQQ00000HbOrB</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>DOSIsoft HW</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>C#89565</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>30008234_CMS001_2</t>
         </is>

--- a/Mass_update_DOSIsoft/mass_update_DOSIsoft_hierarchy_fix.xlsx
+++ b/Mass_update_DOSIsoft/mass_update_DOSIsoft_hierarchy_fix.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,113 +463,113 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>a0RQQ00000MIyyj</t>
+          <t>a0R6g00000DLfxo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>a0R6g00000DLAtn</t>
+          <t>a0R3g0000097RZ0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>a0R6g00000DLAtn</t>
+          <t>a0R3g0000097RZ0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DOSIsoft HW</t>
+          <t>DOSISOFT SW EPIB</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C#89565</t>
+          <t>1550233</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30005138_DOS001_2</t>
+          <t>11261_001_2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>a0RQQ00000MIyyk</t>
+          <t>a0R6g00000DLfxn</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>a0R6g00000DLAtn</t>
+          <t>a0R3g0000097RZ0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>a0R6g00000DLAtn</t>
+          <t>a0R3g0000097RZ0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DOSIsoft HW</t>
+          <t>DOSISOFT SW EPIG</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C#89565</t>
+          <t>1550234</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30005138_DOS001_2</t>
+          <t>11261_001_2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>a0RQQ00000MIyyl</t>
+          <t>a0RQQ00000MVpso</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>a0R6g00000DLAtn</t>
+          <t>a0RKf00000HpZOQ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>a0R6g00000DLAtn</t>
+          <t>a0RKf00000HpZOQ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>THINKQA FOR LINAC</t>
+          <t>DOSIsoft HW</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C#89549-20</t>
+          <t>C#89565</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30005138_DOS001_2</t>
+          <t>11429_DOS001_2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>a0RQQ00000MIyym</t>
+          <t>a0RQQ00000MVpsq</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>a0R6g00000DLAtn</t>
+          <t>a0RKf00000HpZOQ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>a0R6g00000DLAtn</t>
+          <t>a0RKf00000HpZOQ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -584,37 +584,165 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30005138_DOS001_2</t>
+          <t>11429_DOS001_2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>a0RQQ00000MIyyj</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>a0R6g00000DLAtn</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>a0R6g00000DLAtn</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DOSIsoft HW</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>C#89565</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>30005138_DOS001_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MIyyk</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>a0R6g00000DLAtn</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>a0R6g00000DLAtn</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DOSIsoft HW</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>C#89565</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30005138_DOS001_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MIyyl</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>a0R6g00000DLAtn</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>a0R6g00000DLAtn</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>THINKQA FOR LINAC</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>C#89549-20</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>30005138_DOS001_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>a0RQQ00000MIyym</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>a0R6g00000DLAtn</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>a0R6g00000DLAtn</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>THINKQA FOR LINAC</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>C#89549-20</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>30005138_DOS001_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>a0RQQ00000LcAQU</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>a0RQQ00000HbOrB</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>a0RQQ00000HbOrB</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>DOSIsoft HW</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>C#89565</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>30008234_CMS001_2</t>
         </is>
